--- a/0myStrategy/Historical_Volatility.xlsx
+++ b/0myStrategy/Historical_Volatility.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="50">
   <si>
     <t>UnderlyingTicker</t>
   </si>
@@ -31,109 +31,139 @@
     <t>Historical_Volatility</t>
   </si>
   <si>
+    <t>فملي</t>
+  </si>
+  <si>
+    <t>توان</t>
+  </si>
+  <si>
+    <t>اهرم</t>
+  </si>
+  <si>
+    <t>موج</t>
+  </si>
+  <si>
+    <t>ذوب</t>
+  </si>
+  <si>
+    <t>وبملت</t>
+  </si>
+  <si>
     <t>شپنا</t>
   </si>
   <si>
-    <t>توان</t>
-  </si>
-  <si>
-    <t>موج</t>
-  </si>
-  <si>
-    <t>اهرم</t>
-  </si>
-  <si>
     <t>تاصيكو</t>
   </si>
   <si>
-    <t>وبملت</t>
-  </si>
-  <si>
     <t>شستا</t>
   </si>
   <si>
+    <t>وتجارت</t>
+  </si>
+  <si>
+    <t>خودرو</t>
+  </si>
+  <si>
+    <t>هم تراز</t>
+  </si>
+  <si>
+    <t>وبصادر</t>
+  </si>
+  <si>
+    <t>اطلس</t>
+  </si>
+  <si>
     <t>جوانه كوچك</t>
   </si>
   <si>
-    <t>اطلس</t>
-  </si>
-  <si>
-    <t>وتجارت</t>
-  </si>
-  <si>
-    <t>هم تراز</t>
-  </si>
-  <si>
-    <t>خودرو</t>
-  </si>
-  <si>
-    <t>ذوب</t>
-  </si>
-  <si>
-    <t>فملي</t>
-  </si>
-  <si>
-    <t>وبصادر</t>
-  </si>
-  <si>
     <t>طعام</t>
   </si>
   <si>
     <t>فزر</t>
   </si>
   <si>
+    <t>درخشان</t>
+  </si>
+  <si>
+    <t>كهربا</t>
+  </si>
+  <si>
+    <t>طلا</t>
+  </si>
+  <si>
+    <t>جواهر</t>
+  </si>
+  <si>
+    <t>زرگر</t>
+  </si>
+  <si>
+    <t>35425587644337450</t>
+  </si>
+  <si>
+    <t>41927452991671109</t>
+  </si>
+  <si>
+    <t>17914401175772326</t>
+  </si>
+  <si>
+    <t>67141987086032267</t>
+  </si>
+  <si>
+    <t>71483646978964608</t>
+  </si>
+  <si>
+    <t>778253364357513</t>
+  </si>
+  <si>
     <t>7745894403636165</t>
   </si>
   <si>
-    <t>41927452991671109</t>
-  </si>
-  <si>
-    <t>67141987086032267</t>
-  </si>
-  <si>
-    <t>17914401175772326</t>
-  </si>
-  <si>
     <t>23293437377896568</t>
   </si>
   <si>
-    <t>778253364357513</t>
-  </si>
-  <si>
     <t>2400322364771558</t>
   </si>
   <si>
+    <t>63917421733088077</t>
+  </si>
+  <si>
+    <t>65883838195688438</t>
+  </si>
+  <si>
+    <t>51920757918600374</t>
+  </si>
+  <si>
+    <t>28320293733348826</t>
+  </si>
+  <si>
+    <t>11427939669935844</t>
+  </si>
+  <si>
     <t>67455383896188985</t>
   </si>
   <si>
-    <t>11427939669935844</t>
-  </si>
-  <si>
-    <t>63917421733088077</t>
-  </si>
-  <si>
-    <t>51920757918600374</t>
-  </si>
-  <si>
-    <t>65883838195688438</t>
-  </si>
-  <si>
-    <t>71483646978964608</t>
-  </si>
-  <si>
-    <t>35425587644337450</t>
-  </si>
-  <si>
-    <t>28320293733348826</t>
-  </si>
-  <si>
     <t>31230051169165044</t>
   </si>
   <si>
     <t>8175784894140974</t>
   </si>
   <si>
-    <t>1405-04-26</t>
+    <t>61805666737517582</t>
+  </si>
+  <si>
+    <t>25559236668122210</t>
+  </si>
+  <si>
+    <t>46700660505281786</t>
+  </si>
+  <si>
+    <t>38544104313215500</t>
+  </si>
+  <si>
+    <t>16817885126368964</t>
+  </si>
+  <si>
+    <t>1405-05-23</t>
   </si>
 </sst>
 </file>
@@ -491,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -516,16 +546,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E2">
-        <v>0.4778</v>
+        <v>0.7232</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -533,16 +563,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E3">
-        <v>0.4385</v>
+        <v>0.5138</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -550,16 +580,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E4">
-        <v>0.4319</v>
+        <v>0.5026</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -567,16 +597,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E5">
-        <v>0.4255</v>
+        <v>0.5013</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -584,16 +614,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>0.371</v>
+        <v>0.4661</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -601,16 +631,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E7">
-        <v>0.3366</v>
+        <v>0.4496</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -618,16 +648,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E8">
-        <v>0.3305</v>
+        <v>0.4096</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -635,16 +665,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E9">
-        <v>0.3236</v>
+        <v>0.3934</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -652,16 +682,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E10">
-        <v>0.3226</v>
+        <v>0.3831</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -669,16 +699,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E11">
-        <v>0.3213</v>
+        <v>0.379</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -686,16 +716,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E12">
-        <v>0.3207</v>
+        <v>0.3679</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -703,16 +733,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E13">
-        <v>0.3143</v>
+        <v>0.3647</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -720,16 +750,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E14">
-        <v>0.3089</v>
+        <v>0.3608</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -737,16 +767,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E15">
-        <v>0.3054</v>
+        <v>0.3594</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -754,16 +784,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E16">
-        <v>0.3031</v>
+        <v>0.3523</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -771,16 +801,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E17">
-        <v>0.3005</v>
+        <v>0.3389</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -788,16 +818,101 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E18">
-        <v>0.2878</v>
+        <v>0.3229</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19">
+        <v>0.3225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20">
+        <v>0.3198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21">
+        <v>60</v>
+      </c>
+      <c r="D21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21">
+        <v>0.3185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22">
+        <v>0.3104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23">
+        <v>0.2997</v>
       </c>
     </row>
   </sheetData>

--- a/0myStrategy/Historical_Volatility.xlsx
+++ b/0myStrategy/Historical_Volatility.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\python_project\boors\Ekhtiyar\generate_strategyV4\0myStrategy\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C93990-8D34-417D-8CCA-CA728AEACA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -169,8 +180,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,6 +244,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -279,7 +298,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -311,9 +330,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -345,6 +382,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -520,11 +575,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -555,10 +615,10 @@
         <v>49</v>
       </c>
       <c r="E2">
-        <v>0.7232</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>0.72319999999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -572,10 +632,10 @@
         <v>49</v>
       </c>
       <c r="E3">
-        <v>0.5138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>0.51380000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -589,10 +649,10 @@
         <v>49</v>
       </c>
       <c r="E4">
-        <v>0.5026</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>0.50260000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -606,10 +666,10 @@
         <v>49</v>
       </c>
       <c r="E5">
-        <v>0.5013</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>0.50129999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -623,10 +683,10 @@
         <v>49</v>
       </c>
       <c r="E6">
-        <v>0.4661</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>0.46610000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -643,7 +703,7 @@
         <v>0.4496</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -657,10 +717,10 @@
         <v>49</v>
       </c>
       <c r="E8">
-        <v>0.4096</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>0.40960000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -674,10 +734,10 @@
         <v>49</v>
       </c>
       <c r="E9">
-        <v>0.3934</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>0.39340000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -694,7 +754,7 @@
         <v>0.3831</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -711,7 +771,7 @@
         <v>0.379</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -728,7 +788,7 @@
         <v>0.3679</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -742,10 +802,10 @@
         <v>49</v>
       </c>
       <c r="E13">
-        <v>0.3647</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>0.36470000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -759,10 +819,10 @@
         <v>49</v>
       </c>
       <c r="E14">
-        <v>0.3608</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>0.36080000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -779,7 +839,7 @@
         <v>0.3594</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -796,7 +856,7 @@
         <v>0.3523</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -810,10 +870,10 @@
         <v>49</v>
       </c>
       <c r="E17">
-        <v>0.3389</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>0.33889999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -827,10 +887,10 @@
         <v>49</v>
       </c>
       <c r="E18">
-        <v>0.3229</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>0.32290000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -844,10 +904,10 @@
         <v>49</v>
       </c>
       <c r="E19">
-        <v>0.3225</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>0.32250000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -861,10 +921,10 @@
         <v>49</v>
       </c>
       <c r="E20">
-        <v>0.3198</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>0.31979999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -878,10 +938,10 @@
         <v>49</v>
       </c>
       <c r="E21">
-        <v>0.3185</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>0.31850000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -895,10 +955,10 @@
         <v>49</v>
       </c>
       <c r="E22">
-        <v>0.3104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>0.31040000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -912,7 +972,7 @@
         <v>49</v>
       </c>
       <c r="E23">
-        <v>0.2997</v>
+        <v>0.29970000000000002</v>
       </c>
     </row>
   </sheetData>
